--- a/nriss-patch-2/ig/StructureDefinition-fr-advance-directive-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-advance-directive-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -560,7 +560,7 @@
   &lt;coding&gt;
     &lt;system value="http://terminology.hl7.org/CodeSystem/consentscope"/&gt;
     &lt;code value="adr"/&gt;
-    &lt;display value="Advance Directive"/&gt;
+    &lt;display value="Advanced Care Directive"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1339,7 +1339,7 @@
     <t>Typical use of this is a Document code with class = CDA.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-directive-anticipee-cisis|20260619134043</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-directive-anticipee-cisis|20260916095456</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
